--- a/characteristics_tables/RSV_Study_Characteristics.xlsx
+++ b/characteristics_tables/RSV_Study_Characteristics.xlsx
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10 866</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>576 222</t>
+          <t>576222</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>10866</v>
       </c>
     </row>
     <row r="9">
@@ -12561,7 +12561,7 @@
         </is>
       </c>
       <c r="D69">
-        <v>576</v>
+        <v>576222</v>
       </c>
     </row>
     <row r="70">

--- a/characteristics_tables/RSV_Study_Characteristics.xlsx
+++ b/characteristics_tables/RSV_Study_Characteristics.xlsx
@@ -5948,12 +5948,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Observational - with comparator group</t>
+          <t>Non-randomized single arm</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>retrospective cohort</t>
+          <t>only 1 arm eligible, treated as single arm</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">

--- a/characteristics_tables/RSV_Study_Characteristics.xlsx
+++ b/characteristics_tables/RSV_Study_Characteristics.xlsx
@@ -1081,7 +1081,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7">
         <v>1183</v>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B8">
         <v>1257</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9">
         <v>1259</v>
@@ -1407,10 +1407,20 @@
           <t>https://doi.org/10.1093/infdis/jiaf381</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B10">
         <v>1267</v>
@@ -1760,7 +1770,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B13">
         <v>1696</v>
@@ -1883,7 +1893,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B14">
         <v>1710</v>
@@ -2109,7 +2119,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16">
         <v>1833</v>
@@ -2224,10 +2234,20 @@
           <t>https://doi.org/10.1080/21645515.2026.2658377</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17">
         <v>1834</v>
@@ -2340,7 +2360,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B18">
         <v>1970</v>
@@ -2566,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B20">
         <v>2150</v>
@@ -2689,7 +2709,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B21">
         <v>2154</v>
@@ -2792,6 +2812,16 @@
       <c r="X21" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.lanepe.2026.101620</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B23">
         <v>2183</v>
@@ -3008,7 +3038,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B24">
         <v>2204</v>
@@ -3121,7 +3151,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B25">
         <v>2207</v>
@@ -3244,7 +3274,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B26">
         <v>2208</v>
@@ -3964,6 +3994,16 @@
           <t>https://doi.org/10.1097/INF.0000000000004920</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -4817,7 +4857,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Ecological</t>
+          <t>Observational - with comparator group</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -5448,7 +5488,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B45">
         <v>4110</v>
@@ -5566,12 +5606,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>High: D1: Randomization; Some Concerns: D2: Deviations from the intended interventions</t>
+          <t>High: D1: Randomization; High: D2: Deviations from the intended interventions</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>High; Some Concerns</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -5901,6 +5941,16 @@
       <c r="X48" t="inlineStr">
         <is>
           <t>https://doi.org/10.1001/jama.2025.16744</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>No risk of bias data in outcomes sheet</t>
         </is>
       </c>
     </row>
@@ -13131,7 +13181,7 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B154">
         <v>1183</v>
@@ -13154,7 +13204,7 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B155">
         <v>1183</v>
@@ -13177,7 +13227,7 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B156">
         <v>1257</v>
@@ -13200,7 +13250,7 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B157">
         <v>1259</v>
@@ -13223,7 +13273,7 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B158">
         <v>1267</v>
@@ -13246,7 +13296,7 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B159">
         <v>1267</v>
@@ -13269,7 +13319,7 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B160">
         <v>1267</v>
@@ -13292,7 +13342,7 @@
     </row>
     <row r="161">
       <c r="A161">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B161">
         <v>1696</v>
@@ -13315,7 +13365,7 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B162">
         <v>1710</v>
@@ -13338,7 +13388,7 @@
     </row>
     <row r="163">
       <c r="A163">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B163">
         <v>1833</v>
@@ -13361,7 +13411,7 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B164">
         <v>1833</v>
@@ -13384,7 +13434,7 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B165">
         <v>1833</v>
@@ -13407,7 +13457,7 @@
     </row>
     <row r="166">
       <c r="A166">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B166">
         <v>1834</v>
@@ -13430,7 +13480,7 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B167">
         <v>1834</v>
@@ -13453,7 +13503,7 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B168">
         <v>1970</v>
@@ -13476,7 +13526,7 @@
     </row>
     <row r="169">
       <c r="A169">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B169">
         <v>2150</v>
@@ -13499,7 +13549,7 @@
     </row>
     <row r="170">
       <c r="A170">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B170">
         <v>2150</v>
@@ -13522,7 +13572,7 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B171">
         <v>2154</v>
@@ -13545,7 +13595,7 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B172">
         <v>2183</v>
@@ -13568,7 +13618,7 @@
     </row>
     <row r="173">
       <c r="A173">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B173">
         <v>2204</v>
@@ -13591,7 +13641,7 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B174">
         <v>2207</v>
@@ -13614,7 +13664,7 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B175">
         <v>2208</v>
@@ -13637,7 +13687,7 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B176">
         <v>2208</v>
@@ -13660,7 +13710,7 @@
     </row>
     <row r="177">
       <c r="A177">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B177">
         <v>2208</v>
@@ -13683,7 +13733,7 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B178">
         <v>4110</v>
@@ -13706,7 +13756,7 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B179">
         <v>4110</v>
@@ -13729,7 +13779,7 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B180">
         <v>4110</v>
@@ -13864,7 +13914,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7">
         <v>1183</v>
@@ -13880,7 +13930,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B8">
         <v>1259</v>
@@ -13896,7 +13946,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9">
         <v>1267</v>
@@ -13944,7 +13994,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B12">
         <v>1696</v>
@@ -13976,7 +14026,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B14">
         <v>1833</v>
@@ -13992,7 +14042,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B15">
         <v>1834</v>
@@ -14008,7 +14058,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B16">
         <v>1970</v>
@@ -14040,7 +14090,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B18">
         <v>2150</v>
@@ -14056,7 +14106,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B19">
         <v>2154</v>
@@ -14072,7 +14122,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20">
         <v>2183</v>
@@ -14088,7 +14138,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B21">
         <v>2204</v>
@@ -14104,7 +14154,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B22">
         <v>2207</v>
@@ -14120,7 +14170,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B23">
         <v>2208</v>
@@ -14392,7 +14442,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B40">
         <v>4110</v>
@@ -15170,7 +15220,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B15">
         <v>1183</v>
@@ -15188,7 +15238,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16">
         <v>1183</v>
@@ -15206,7 +15256,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B17">
         <v>1183</v>
@@ -15224,7 +15274,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B18">
         <v>1183</v>
@@ -15242,7 +15292,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B19">
         <v>1257</v>
@@ -15260,7 +15310,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B20">
         <v>1257</v>
@@ -15278,7 +15328,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21">
         <v>1257</v>
@@ -15296,7 +15346,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22">
         <v>1257</v>
@@ -15314,7 +15364,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23">
         <v>1259</v>
@@ -15332,7 +15382,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24">
         <v>1259</v>
@@ -15350,7 +15400,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25">
         <v>1259</v>
@@ -15368,7 +15418,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26">
         <v>1267</v>
@@ -15386,7 +15436,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B27">
         <v>1267</v>
@@ -15458,7 +15508,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31">
         <v>1696</v>
@@ -15476,7 +15526,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B32">
         <v>1710</v>
@@ -15512,7 +15562,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B34">
         <v>1833</v>
@@ -15530,7 +15580,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B35">
         <v>1833</v>
@@ -15548,7 +15598,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B36">
         <v>1834</v>
@@ -15566,7 +15616,7 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B37">
         <v>1834</v>
@@ -15584,7 +15634,7 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B38">
         <v>1970</v>
@@ -15602,7 +15652,7 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B39">
         <v>1970</v>
@@ -15638,7 +15688,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B41">
         <v>2150</v>
@@ -15656,7 +15706,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B42">
         <v>2150</v>
@@ -15674,7 +15724,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B43">
         <v>2154</v>
@@ -15782,7 +15832,7 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B49">
         <v>2183</v>
@@ -15800,7 +15850,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B50">
         <v>2204</v>
@@ -15818,7 +15868,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B51">
         <v>2207</v>
@@ -15836,7 +15886,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B52">
         <v>2207</v>
@@ -15854,7 +15904,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B53">
         <v>2207</v>
@@ -15872,7 +15922,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B54">
         <v>2207</v>
@@ -15890,7 +15940,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B55">
         <v>2208</v>
@@ -15908,7 +15958,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B56">
         <v>2208</v>
@@ -16574,7 +16624,7 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B93">
         <v>4110</v>
@@ -17812,7 +17862,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7">
         <v>1183</v>
@@ -17830,7 +17880,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8">
         <v>1183</v>
@@ -17848,7 +17898,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9">
         <v>1183</v>
@@ -17866,7 +17916,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B10">
         <v>1257</v>
@@ -17884,7 +17934,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11">
         <v>1257</v>
@@ -17902,7 +17952,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12">
         <v>1259</v>
@@ -17920,7 +17970,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13">
         <v>1259</v>
@@ -17938,7 +17988,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14">
         <v>1267</v>
@@ -17992,7 +18042,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B17">
         <v>1696</v>
@@ -18010,7 +18060,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18">
         <v>1710</v>
@@ -18046,7 +18096,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B20">
         <v>1833</v>
@@ -18064,7 +18114,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B21">
         <v>1834</v>
@@ -18082,7 +18132,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B22">
         <v>1970</v>
@@ -18100,7 +18150,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B23">
         <v>1970</v>
@@ -18118,7 +18168,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B24">
         <v>1970</v>
@@ -18154,7 +18204,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B26">
         <v>2150</v>
@@ -18172,7 +18222,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B27">
         <v>2150</v>
@@ -18190,7 +18240,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B28">
         <v>2150</v>
@@ -18208,7 +18258,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B29">
         <v>2154</v>
@@ -18244,7 +18294,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B31">
         <v>2183</v>
@@ -18262,7 +18312,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B32">
         <v>2204</v>
@@ -18280,7 +18330,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33">
         <v>2207</v>
@@ -18298,7 +18348,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34">
         <v>2208</v>
@@ -18658,7 +18708,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B54">
         <v>4110</v>
@@ -18676,7 +18726,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B55">
         <v>4110</v>
@@ -26663,7 +26713,7 @@
     </row>
     <row r="323">
       <c r="A323">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B323">
         <v>1183</v>
@@ -26686,7 +26736,7 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B324">
         <v>1183</v>
@@ -26709,7 +26759,7 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B325">
         <v>1183</v>
@@ -26732,7 +26782,7 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B326">
         <v>1183</v>
@@ -26755,7 +26805,7 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B327">
         <v>1183</v>
@@ -26778,7 +26828,7 @@
     </row>
     <row r="328">
       <c r="A328">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B328">
         <v>1183</v>
@@ -26801,7 +26851,7 @@
     </row>
     <row r="329">
       <c r="A329">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B329">
         <v>1183</v>
@@ -26824,7 +26874,7 @@
     </row>
     <row r="330">
       <c r="A330">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B330">
         <v>1183</v>
@@ -26847,7 +26897,7 @@
     </row>
     <row r="331">
       <c r="A331">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B331">
         <v>1183</v>
@@ -26870,7 +26920,7 @@
     </row>
     <row r="332">
       <c r="A332">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B332">
         <v>1257</v>
@@ -26893,7 +26943,7 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B333">
         <v>1257</v>
@@ -26916,7 +26966,7 @@
     </row>
     <row r="334">
       <c r="A334">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B334">
         <v>1257</v>
@@ -26939,7 +26989,7 @@
     </row>
     <row r="335">
       <c r="A335">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B335">
         <v>1257</v>
@@ -26962,7 +27012,7 @@
     </row>
     <row r="336">
       <c r="A336">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B336">
         <v>1257</v>
@@ -26985,7 +27035,7 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B337">
         <v>1257</v>
@@ -27008,7 +27058,7 @@
     </row>
     <row r="338">
       <c r="A338">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B338">
         <v>1257</v>
@@ -27031,7 +27081,7 @@
     </row>
     <row r="339">
       <c r="A339">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B339">
         <v>1257</v>
@@ -27054,7 +27104,7 @@
     </row>
     <row r="340">
       <c r="A340">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B340">
         <v>1257</v>
@@ -27077,7 +27127,7 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B341">
         <v>1257</v>
@@ -27100,7 +27150,7 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B342">
         <v>1257</v>
@@ -27123,7 +27173,7 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B343">
         <v>1257</v>
@@ -27146,7 +27196,7 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B344">
         <v>1267</v>
@@ -27169,7 +27219,7 @@
     </row>
     <row r="345">
       <c r="A345">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B345">
         <v>1267</v>
@@ -27192,7 +27242,7 @@
     </row>
     <row r="346">
       <c r="A346">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B346">
         <v>1267</v>
@@ -27215,7 +27265,7 @@
     </row>
     <row r="347">
       <c r="A347">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B347">
         <v>1267</v>
@@ -27238,7 +27288,7 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B348">
         <v>1267</v>
@@ -27261,7 +27311,7 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B349">
         <v>1267</v>
@@ -27284,7 +27334,7 @@
     </row>
     <row r="350">
       <c r="A350">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B350">
         <v>1696</v>
@@ -27307,7 +27357,7 @@
     </row>
     <row r="351">
       <c r="A351">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B351">
         <v>1710</v>
@@ -27330,7 +27380,7 @@
     </row>
     <row r="352">
       <c r="A352">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B352">
         <v>1834</v>
@@ -27353,7 +27403,7 @@
     </row>
     <row r="353">
       <c r="A353">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B353">
         <v>1834</v>
@@ -27376,7 +27426,7 @@
     </row>
     <row r="354">
       <c r="A354">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B354">
         <v>1834</v>
@@ -27399,7 +27449,7 @@
     </row>
     <row r="355">
       <c r="A355">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B355">
         <v>1970</v>
@@ -27422,7 +27472,7 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B356">
         <v>1970</v>
@@ -27445,7 +27495,7 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B357">
         <v>1970</v>
@@ -27468,7 +27518,7 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B358">
         <v>2150</v>
@@ -27491,7 +27541,7 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B359">
         <v>2150</v>
@@ -27514,7 +27564,7 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B360">
         <v>2150</v>
@@ -27537,7 +27587,7 @@
     </row>
     <row r="361">
       <c r="A361">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B361">
         <v>2150</v>
@@ -27560,7 +27610,7 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B362">
         <v>2150</v>
@@ -27583,7 +27633,7 @@
     </row>
     <row r="363">
       <c r="A363">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B363">
         <v>2150</v>
@@ -27606,7 +27656,7 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B364">
         <v>2150</v>
@@ -27629,7 +27679,7 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B365">
         <v>2150</v>
@@ -27652,7 +27702,7 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B366">
         <v>2150</v>
@@ -27675,7 +27725,7 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B367">
         <v>2150</v>
@@ -27698,7 +27748,7 @@
     </row>
     <row r="368">
       <c r="A368">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B368">
         <v>2150</v>
@@ -27721,7 +27771,7 @@
     </row>
     <row r="369">
       <c r="A369">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B369">
         <v>2150</v>
@@ -27744,7 +27794,7 @@
     </row>
     <row r="370">
       <c r="A370">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B370">
         <v>2183</v>
@@ -27767,7 +27817,7 @@
     </row>
     <row r="371">
       <c r="A371">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B371">
         <v>2183</v>
@@ -27790,7 +27840,7 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B372">
         <v>2183</v>
@@ -27813,7 +27863,7 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B373">
         <v>2183</v>
@@ -27836,7 +27886,7 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B374">
         <v>2183</v>
@@ -27859,7 +27909,7 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B375">
         <v>2204</v>
@@ -27877,7 +27927,7 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B376">
         <v>2204</v>
@@ -27895,7 +27945,7 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B377">
         <v>2204</v>
@@ -27913,7 +27963,7 @@
     </row>
     <row r="378">
       <c r="A378">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B378">
         <v>2204</v>
@@ -27931,7 +27981,7 @@
     </row>
     <row r="379">
       <c r="A379">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B379">
         <v>2204</v>
@@ -27949,7 +27999,7 @@
     </row>
     <row r="380">
       <c r="A380">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B380">
         <v>2207</v>
@@ -27972,7 +28022,7 @@
     </row>
     <row r="381">
       <c r="A381">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B381">
         <v>2207</v>
@@ -27995,7 +28045,7 @@
     </row>
     <row r="382">
       <c r="A382">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B382">
         <v>2207</v>
@@ -28018,7 +28068,7 @@
     </row>
     <row r="383">
       <c r="A383">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B383">
         <v>2207</v>
@@ -28041,7 +28091,7 @@
     </row>
     <row r="384">
       <c r="A384">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B384">
         <v>2207</v>
@@ -28064,7 +28114,7 @@
     </row>
     <row r="385">
       <c r="A385">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B385">
         <v>2207</v>
@@ -28087,7 +28137,7 @@
     </row>
     <row r="386">
       <c r="A386">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B386">
         <v>2207</v>
@@ -28110,7 +28160,7 @@
     </row>
     <row r="387">
       <c r="A387">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B387">
         <v>2207</v>
@@ -28133,7 +28183,7 @@
     </row>
     <row r="388">
       <c r="A388">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B388">
         <v>2208</v>
@@ -28156,7 +28206,7 @@
     </row>
     <row r="389">
       <c r="A389">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B389">
         <v>2208</v>
@@ -28179,7 +28229,7 @@
     </row>
     <row r="390">
       <c r="A390">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B390">
         <v>2208</v>
@@ -28202,7 +28252,7 @@
     </row>
     <row r="391">
       <c r="A391">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B391">
         <v>4110</v>
@@ -28225,7 +28275,7 @@
     </row>
     <row r="392">
       <c r="A392">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B392">
         <v>4110</v>
@@ -28248,7 +28298,7 @@
     </row>
     <row r="393">
       <c r="A393">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B393">
         <v>4110</v>
@@ -28271,7 +28321,7 @@
     </row>
     <row r="394">
       <c r="A394">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B394">
         <v>4110</v>
@@ -28283,7 +28333,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">

--- a/characteristics_tables/RSV_Study_Characteristics.xlsx
+++ b/characteristics_tables/RSV_Study_Characteristics.xlsx
@@ -591,12 +591,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Critical: D1: Confounding</t>
+          <t>Not Assessed Due to Study Design: D1: Confounding</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fonseca 2026</t>
+          <t>Fonseca 2026 (b)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3482,16 +3482,6 @@
           <t>Effectiveness: Disease-related hospitalization or ED visits, Lab-confirmed infection or illness, Disease-specific mortality</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Effectiveness: Disease-related hospitalization or ED visits, Lab-confirmed infection or illness, Disease-specific mortality</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Effectiveness</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>GSK funded this study [GSK study identifier: 300432]</t>
@@ -3519,12 +3509,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Moderate: awaiting domain decision</t>
+          <t>No risk of bias data in outcomes sheet</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>No risk of bias data in outcomes sheet</t>
         </is>
       </c>
     </row>
@@ -5493,12 +5483,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>High: D1: Randomization; High: D2: Deviations from the intended interventions</t>
+          <t>Some Concerns: awaiting domain decision</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some Concerns</t>
         </is>
       </c>
     </row>
@@ -7537,7 +7527,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>RSV</t>
+          <t>Influenza, RSV</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -10333,7 +10323,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fonseca 2026</t>
+          <t>Fonseca 2026 (b)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -10356,7 +10346,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fonseca 2026</t>
+          <t>Fonseca 2026 (b)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -10379,7 +10369,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fonseca 2026</t>
+          <t>Fonseca 2026 (b)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -14084,7 +14074,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fonseca 2026</t>
+          <t>Fonseca 2026 (b)</t>
         </is>
       </c>
       <c r="D26">
@@ -15892,7 +15882,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fonseca 2026</t>
+          <t>Fonseca 2026 (b)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -17618,7 +17608,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -18246,7 +18236,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fonseca 2026</t>
+          <t>Fonseca 2026 (b)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -18935,20 +18925,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RSV</t>
+          <t>Influenza</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="B74">
-        <v>66</v>
+        <v>645</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Amarin 2026</t>
+          <t>Singer 2025</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -18959,14 +18949,14 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="B75">
-        <v>664</v>
+        <v>66</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Stowe 2025</t>
+          <t>Amarin 2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -18977,14 +18967,14 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B76">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Strautins 2026</t>
+          <t>Stowe 2025</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -18995,14 +18985,14 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B77">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Surie 2025</t>
+          <t>Strautins 2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -19013,14 +19003,14 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B78">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Symes 2026</t>
+          <t>Surie 2025</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -19031,14 +19021,14 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B79">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tartof 2026</t>
+          <t>Symes 2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -19049,19 +19039,19 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B80">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Toepfer 2025</t>
+          <t>Tartof 2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>COVID</t>
+          <t>RSV</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19069,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>COVID</t>
         </is>
       </c>
     </row>
@@ -19097,25 +19087,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>RSV</t>
+          <t>Influenza</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="B83">
-        <v>71</v>
+        <v>703</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Andersen 2025</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>COVID</t>
+          <t>RSV</t>
         </is>
       </c>
     </row>
@@ -19133,7 +19123,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>COVID</t>
         </is>
       </c>
     </row>
@@ -19151,20 +19141,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>RSV</t>
+          <t>Influenza</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="B86">
-        <v>739</v>
+        <v>71</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wiegand 2026</t>
+          <t>Andersen 2025</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -19175,14 +19165,14 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B87">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Xu 2026</t>
+          <t>Wiegand 2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -19193,14 +19183,14 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B88">
-        <v>774</v>
+        <v>755</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Zambrano 2025</t>
+          <t>Xu 2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -19211,14 +19201,14 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="B89">
-        <v>82</v>
+        <v>774</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Attaianese 2025</t>
+          <t>Zambrano 2025</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -19229,14 +19219,14 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B90">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bajema 2026</t>
+          <t>Attaianese 2025</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -19247,14 +19237,14 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B91">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bao 2025</t>
+          <t>Bajema 2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -19265,17 +19255,35 @@
     </row>
     <row r="92">
       <c r="A92">
+        <v>9</v>
+      </c>
+      <c r="B92">
+        <v>91</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bao 2025</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>RSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
         <v>85</v>
       </c>
-      <c r="B92">
+      <c r="B93">
         <v>951</v>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Gabet 2026</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>RSV</t>
         </is>
@@ -19288,7 +19296,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E411"/>
+  <dimension ref="A1:E412"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -20482,7 +20490,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -20505,7 +20513,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20528,7 +20536,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20551,7 +20559,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20574,7 +20582,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20597,7 +20605,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20620,7 +20628,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -20643,7 +20651,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20666,7 +20674,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -20689,7 +20697,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Not Assessed Due to Study Design</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -25368,14 +25376,14 @@
     </row>
     <row r="268">
       <c r="A268">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B268">
-        <v>664</v>
+        <v>645</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Stowe 2025</t>
+          <t>Singer 2025</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -25391,14 +25399,14 @@
     </row>
     <row r="269">
       <c r="A269">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B269">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Strautins 2026</t>
+          <t>Singer 2025</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -25414,19 +25422,19 @@
     </row>
     <row r="270">
       <c r="A270">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B270">
-        <v>674</v>
+        <v>645</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Surie 2025</t>
+          <t>Singer 2025</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -25437,19 +25445,19 @@
     </row>
     <row r="271">
       <c r="A271">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B271">
-        <v>674</v>
+        <v>645</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Surie 2025</t>
+          <t>Singer 2025</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Serious</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -25460,14 +25468,14 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B272">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Symes 2026</t>
+          <t>Stowe 2025</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -25483,14 +25491,14 @@
     </row>
     <row r="273">
       <c r="A273">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B273">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Symes 2026</t>
+          <t>Strautins 2026</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -25506,19 +25514,19 @@
     </row>
     <row r="274">
       <c r="A274">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B274">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Symes 2026</t>
+          <t>Surie 2025</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Serious</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -25529,73 +25537,93 @@
     </row>
     <row r="275">
       <c r="A275">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B275">
-        <v>689</v>
+        <v>674</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Tartof 2026</t>
+          <t>Surie 2025</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+          <t>Serious</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B276">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Tartof 2026</t>
+          <t>Symes 2026</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B277">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Tartof 2026</t>
+          <t>Symes 2026</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B278">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Tartof 2026</t>
+          <t>Symes 2026</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -25655,93 +25683,73 @@
     </row>
     <row r="282">
       <c r="A282">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B282">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Toepfer 2025</t>
+          <t>Tartof 2026</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B283">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Toepfer 2025</t>
+          <t>Tartof 2026</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B284">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Toepfer 2025</t>
+          <t>Tartof 2026</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B285">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Toepfer 2025</t>
+          <t>Tartof 2026</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>D1: Confounding</t>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
       </c>
     </row>
@@ -25793,116 +25801,116 @@
     </row>
     <row r="288">
       <c r="A288">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B288">
-        <v>739</v>
+        <v>703</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Wiegand 2026</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>D2: Classification of Interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B289">
-        <v>739</v>
+        <v>703</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Wiegand 2026</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>D2: Classification of Interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B290">
-        <v>739</v>
+        <v>703</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Wiegand 2026</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>D2: Classification of Interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B291">
-        <v>739</v>
+        <v>703</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Wiegand 2026</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>D2: Classification of Interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B292">
-        <v>739</v>
+        <v>703</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Wiegand 2026</t>
+          <t>Toepfer 2025</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>D2: Classification of Interventions</t>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
@@ -26069,104 +26077,129 @@
     </row>
     <row r="300">
       <c r="A300">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B300">
-        <v>774</v>
+        <v>739</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Zambrano 2025</t>
+          <t>Wiegand 2026</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>D2: Classification of Interventions</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B301">
-        <v>774</v>
+        <v>739</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Zambrano 2025</t>
+          <t>Wiegand 2026</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>D2: Classification of Interventions</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B302">
-        <v>951</v>
+        <v>739</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Gabet 2026</t>
+          <t>Wiegand 2026</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>D2: Classification of Interventions</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B303">
-        <v>951</v>
+        <v>739</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Gabet 2026</t>
+          <t>Wiegand 2026</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>D2: Classification of Interventions</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B304">
-        <v>951</v>
+        <v>739</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Gabet 2026</t>
+          <t>Wiegand 2026</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>D2: Classification of Interventions</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B305">
-        <v>951</v>
+        <v>774</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Gabet 2026</t>
+          <t>Zambrano 2025</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -26177,116 +26210,91 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B306">
-        <v>1075</v>
+        <v>774</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Zambrano 2025</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>D5: Selection of the reported result</t>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B307">
-        <v>1075</v>
+        <v>951</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Gabet 2026</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>D5: Selection of the reported result</t>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B308">
-        <v>1075</v>
+        <v>951</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Gabet 2026</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>D5: Selection of the reported result</t>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B309">
-        <v>1075</v>
+        <v>951</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Gabet 2026</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>D5: Selection of the reported result</t>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B310">
-        <v>1075</v>
+        <v>951</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Leroux-Roels 2026</t>
+          <t>Gabet 2026</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>D5: Selection of the reported result</t>
+          <t>Low risk of bias (except for concerns about uncontrolled confounding)</t>
         </is>
       </c>
     </row>
@@ -26315,129 +26323,129 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B312">
-        <v>1126</v>
+        <v>1075</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>McLaughlin 2025</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D5: Selection of the reported result</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B313">
-        <v>1126</v>
+        <v>1075</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>McLaughlin 2025</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D5: Selection of the reported result</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B314">
-        <v>1126</v>
+        <v>1075</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>McLaughlin 2025</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D5: Selection of the reported result</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B315">
-        <v>1126</v>
+        <v>1075</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>McLaughlin 2025</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D5: Selection of the reported result</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B316">
-        <v>1126</v>
+        <v>1075</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>McLaughlin 2025</t>
+          <t>Leroux-Roels 2026</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>D1: Confounding</t>
+          <t>D5: Selection of the reported result</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B317">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Michnick 2026</t>
+          <t>McLaughlin 2025</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -26453,14 +26461,14 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B318">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Michnick 2026</t>
+          <t>McLaughlin 2025</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -26476,14 +26484,14 @@
     </row>
     <row r="319">
       <c r="A319">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B319">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Michnick 2026</t>
+          <t>McLaughlin 2025</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -26499,14 +26507,14 @@
     </row>
     <row r="320">
       <c r="A320">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B320">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Michnick 2026</t>
+          <t>McLaughlin 2025</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -26522,14 +26530,14 @@
     </row>
     <row r="321">
       <c r="A321">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B321">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Michnick 2026</t>
+          <t>McLaughlin 2025</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -26591,14 +26599,14 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B324">
-        <v>1183</v>
+        <v>1134</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Parker 2025</t>
+          <t>Michnick 2026</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -26614,14 +26622,14 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B325">
-        <v>1183</v>
+        <v>1134</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Parker 2025</t>
+          <t>Michnick 2026</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -26637,14 +26645,14 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B326">
-        <v>1183</v>
+        <v>1134</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Parker 2025</t>
+          <t>Michnick 2026</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -26660,14 +26668,14 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B327">
-        <v>1183</v>
+        <v>1134</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Parker 2025</t>
+          <t>Michnick 2026</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -26683,14 +26691,14 @@
     </row>
     <row r="328">
       <c r="A328">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B328">
-        <v>1183</v>
+        <v>1134</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Parker 2025</t>
+          <t>Michnick 2026</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -26798,14 +26806,14 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B333">
-        <v>1257</v>
+        <v>1183</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Silk 2026</t>
+          <t>Parker 2025</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -26821,14 +26829,14 @@
     </row>
     <row r="334">
       <c r="A334">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B334">
-        <v>1257</v>
+        <v>1183</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Silk 2026</t>
+          <t>Parker 2025</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -26844,14 +26852,14 @@
     </row>
     <row r="335">
       <c r="A335">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B335">
-        <v>1257</v>
+        <v>1183</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Silk 2026</t>
+          <t>Parker 2025</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -26867,14 +26875,14 @@
     </row>
     <row r="336">
       <c r="A336">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B336">
-        <v>1257</v>
+        <v>1183</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Silk 2026</t>
+          <t>Parker 2025</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -26890,14 +26898,14 @@
     </row>
     <row r="337">
       <c r="A337">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B337">
-        <v>1257</v>
+        <v>1183</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Silk 2026</t>
+          <t>Parker 2025</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -27074,14 +27082,14 @@
     </row>
     <row r="345">
       <c r="A345">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B345">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Simoes 2026</t>
+          <t>Silk 2026</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -27097,14 +27105,14 @@
     </row>
     <row r="346">
       <c r="A346">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B346">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Simoes 2026</t>
+          <t>Silk 2026</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -27120,14 +27128,14 @@
     </row>
     <row r="347">
       <c r="A347">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B347">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Simoes 2026</t>
+          <t>Silk 2026</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -27143,14 +27151,14 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B348">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Simoes 2026</t>
+          <t>Silk 2026</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -27166,14 +27174,14 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B349">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Simoes 2026</t>
+          <t>Silk 2026</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -27442,14 +27450,14 @@
     </row>
     <row r="361">
       <c r="A361">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B361">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Solsman 2026</t>
+          <t>Simoes 2026</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -27465,14 +27473,14 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B362">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Solsman 2026</t>
+          <t>Simoes 2026</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -27488,14 +27496,14 @@
     </row>
     <row r="363">
       <c r="A363">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B363">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Solsman 2026</t>
+          <t>Simoes 2026</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -27511,14 +27519,14 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B364">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Solsman 2026</t>
+          <t>Simoes 2026</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -27534,14 +27542,14 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B365">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Solsman 2026</t>
+          <t>Simoes 2026</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -27580,14 +27588,14 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B367">
-        <v>1696</v>
+        <v>1267</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Bailey 2026</t>
+          <t>Solsman 2026</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -27603,14 +27611,14 @@
     </row>
     <row r="368">
       <c r="A368">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B368">
-        <v>1710</v>
+        <v>1267</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Liang 2026</t>
+          <t>Solsman 2026</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -27626,14 +27634,14 @@
     </row>
     <row r="369">
       <c r="A369">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B369">
-        <v>1834</v>
+        <v>1267</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Goswami 2026</t>
+          <t>Solsman 2026</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -27649,14 +27657,14 @@
     </row>
     <row r="370">
       <c r="A370">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B370">
-        <v>1834</v>
+        <v>1267</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Goswami 2026</t>
+          <t>Solsman 2026</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -27672,14 +27680,14 @@
     </row>
     <row r="371">
       <c r="A371">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B371">
-        <v>1834</v>
+        <v>1267</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Goswami 2026</t>
+          <t>Solsman 2026</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -27695,14 +27703,14 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B372">
-        <v>1970</v>
+        <v>1696</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Wei 2025</t>
+          <t>Bailey 2026</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -27718,14 +27726,14 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B373">
-        <v>1970</v>
+        <v>1710</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Wei 2025</t>
+          <t>Liang 2026</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -27741,14 +27749,14 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B374">
-        <v>1970</v>
+        <v>1834</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Wei 2025</t>
+          <t>Goswami 2026</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -27764,14 +27772,14 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B375">
-        <v>2150</v>
+        <v>1834</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Goswami 2026</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -27787,14 +27795,14 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B376">
-        <v>2150</v>
+        <v>1834</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Goswami 2026</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -27810,14 +27818,14 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B377">
-        <v>2150</v>
+        <v>1970</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Wei 2025</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -27833,14 +27841,14 @@
     </row>
     <row r="378">
       <c r="A378">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B378">
-        <v>2150</v>
+        <v>1970</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Wei 2025</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -27856,14 +27864,14 @@
     </row>
     <row r="379">
       <c r="A379">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B379">
-        <v>2150</v>
+        <v>1970</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Grubber 2026</t>
+          <t>Wei 2025</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -28040,14 +28048,14 @@
     </row>
     <row r="387">
       <c r="A387">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B387">
-        <v>2183</v>
+        <v>2150</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Rick 2026</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -28063,14 +28071,14 @@
     </row>
     <row r="388">
       <c r="A388">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B388">
-        <v>2183</v>
+        <v>2150</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Rick 2026</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -28086,14 +28094,14 @@
     </row>
     <row r="389">
       <c r="A389">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B389">
-        <v>2183</v>
+        <v>2150</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Rick 2026</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -28109,14 +28117,14 @@
     </row>
     <row r="390">
       <c r="A390">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B390">
-        <v>2183</v>
+        <v>2150</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Rick 2026</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -28132,14 +28140,14 @@
     </row>
     <row r="391">
       <c r="A391">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B391">
-        <v>2183</v>
+        <v>2150</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Rick 2026</t>
+          <t>Grubber 2026</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -28155,206 +28163,206 @@
     </row>
     <row r="392">
       <c r="A392">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B392">
-        <v>2204</v>
+        <v>2183</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Duus 2026</t>
+          <t>Rick 2026</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B393">
-        <v>2204</v>
+        <v>2183</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Duus 2026</t>
+          <t>Rick 2026</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B394">
-        <v>2204</v>
+        <v>2183</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Duus 2026</t>
+          <t>Rick 2026</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B395">
-        <v>2204</v>
+        <v>2183</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Duus 2026</t>
+          <t>Rick 2026</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B396">
-        <v>2204</v>
+        <v>2183</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Duus 2026</t>
+          <t>Rick 2026</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>D1: Confounding</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B397">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Rostad 2026</t>
+          <t>Duus 2026</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B398">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Rostad 2026</t>
+          <t>Duus 2026</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B399">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Rostad 2026</t>
+          <t>Duus 2026</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B400">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Rostad 2026</t>
+          <t>Duus 2026</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B401">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Rostad 2026</t>
+          <t>Duus 2026</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -28429,83 +28437,83 @@
     </row>
     <row r="405">
       <c r="A405">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B405">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Roussy 2026</t>
+          <t>Rostad 2026</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>D4: Measurement of the outcome</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B406">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Roussy 2026</t>
+          <t>Rostad 2026</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>D4: Measurement of the outcome</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B407">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Roussy 2026</t>
+          <t>Rostad 2026</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Some Concerns</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>D4: Measurement of the outcome</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B408">
-        <v>4110</v>
+        <v>2207</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Rostad 2026</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -28515,20 +28523,20 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>D1: Randomization</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B409">
-        <v>4110</v>
+        <v>2207</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Rostad 2026</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -28538,53 +28546,76 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>D1: Randomization</t>
+          <t>D2: Deviations from the intended interventions</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B410">
-        <v>4110</v>
+        <v>2208</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Roussy 2026</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>D1: Randomization</t>
+          <t>D4: Measurement of the outcome</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B411">
-        <v>4110</v>
+        <v>2208</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Comstock 2026</t>
+          <t>Roussy 2026</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Some Concerns</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>D2: Deviations from the intended interventions</t>
+          <t>D4: Measurement of the outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412">
+        <v>125</v>
+      </c>
+      <c r="B412">
+        <v>2208</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Roussy 2026</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Some Concerns</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>D4: Measurement of the outcome</t>
         </is>
       </c>
     </row>
